--- a/altas/cotizador.xlsx
+++ b/altas/cotizador.xlsx
@@ -490,25 +490,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="3">
-        <v>122675</v>
+        <v>125006</v>
       </c>
       <c r="C2" s="3">
-        <v>157565</v>
+        <v>160559</v>
       </c>
       <c r="D2" s="3">
-        <v>207359</v>
+        <v>211299</v>
       </c>
       <c r="E2" s="3">
-        <v>351532</v>
+        <v>358211</v>
       </c>
       <c r="F2" s="3">
-        <v>606839</v>
+        <v>618369</v>
       </c>
       <c r="G2" s="3">
-        <v>106841</v>
+        <v>108871</v>
       </c>
       <c r="H2" s="3">
-        <v>92159</v>
+        <v>93910</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -516,25 +516,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="3">
-        <v>123210</v>
+        <v>125551</v>
       </c>
       <c r="C3" s="3">
-        <v>169399</v>
+        <v>172618</v>
       </c>
       <c r="D3" s="3">
-        <v>209322</v>
+        <v>213299</v>
       </c>
       <c r="E3" s="3">
-        <v>361209</v>
+        <v>368072</v>
       </c>
       <c r="F3" s="3">
-        <v>608717</v>
+        <v>620283</v>
       </c>
       <c r="G3" s="3">
-        <v>107120</v>
+        <v>109155</v>
       </c>
       <c r="H3" s="3">
-        <v>92523</v>
+        <v>94281</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -542,25 +542,25 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>138598</v>
+        <v>141231</v>
       </c>
       <c r="C4" s="3">
-        <v>169743</v>
+        <v>172968</v>
       </c>
       <c r="D4" s="3">
-        <v>235865</v>
+        <v>240346</v>
       </c>
       <c r="E4" s="3">
-        <v>406564</v>
+        <v>414289</v>
       </c>
       <c r="F4" s="3">
-        <v>685392</v>
+        <v>698414</v>
       </c>
       <c r="G4" s="3">
-        <v>120380</v>
+        <v>122667</v>
       </c>
       <c r="H4" s="3">
-        <v>104361</v>
+        <v>106344</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -568,25 +568,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="3">
-        <v>195636</v>
+        <v>199353</v>
       </c>
       <c r="C5" s="3">
-        <v>279720</v>
+        <v>285035</v>
       </c>
       <c r="D5" s="3">
-        <v>327638</v>
+        <v>333863</v>
       </c>
       <c r="E5" s="3">
-        <v>549043</v>
+        <v>559475</v>
       </c>
       <c r="F5" s="3">
-        <v>817529</v>
+        <v>833062</v>
       </c>
       <c r="G5" s="3">
-        <v>170657</v>
+        <v>173899</v>
       </c>
       <c r="H5" s="3">
-        <v>148439</v>
+        <v>151259</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -594,25 +594,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>336386</v>
+        <v>342777</v>
       </c>
       <c r="C6" s="3">
-        <v>448079</v>
+        <v>456593</v>
       </c>
       <c r="D6" s="3">
-        <v>589747</v>
+        <v>600952</v>
       </c>
       <c r="E6" s="3">
-        <v>821997</v>
+        <v>837615</v>
       </c>
       <c r="F6" s="3">
-        <v>1120161</v>
+        <v>1141444</v>
       </c>
       <c r="G6" s="3">
-        <v>294749</v>
+        <v>300349</v>
       </c>
       <c r="H6" s="3">
-        <v>257241</v>
+        <v>262129</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -620,25 +620,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="3">
-        <v>87972</v>
+        <v>89643</v>
       </c>
       <c r="C7" s="3">
-        <v>120450</v>
+        <v>122739</v>
       </c>
       <c r="D7" s="3">
-        <v>157433</v>
+        <v>160424</v>
       </c>
       <c r="E7" s="3">
-        <v>297566</v>
+        <v>303220</v>
       </c>
       <c r="F7" s="3">
-        <v>434135</v>
+        <v>442384</v>
       </c>
       <c r="G7" s="3">
-        <v>83626</v>
+        <v>85215</v>
       </c>
       <c r="H7" s="3">
-        <v>75262</v>
+        <v>76692</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -646,25 +646,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>89622</v>
+        <v>91325</v>
       </c>
       <c r="C8" s="3">
-        <v>121640</v>
+        <v>123951</v>
       </c>
       <c r="D8" s="3">
-        <v>157385</v>
+        <v>160375</v>
       </c>
       <c r="E8" s="3">
-        <v>300016</v>
+        <v>305716</v>
       </c>
       <c r="F8" s="3">
-        <v>442194</v>
+        <v>450596</v>
       </c>
       <c r="G8" s="3">
-        <v>83225</v>
+        <v>84806</v>
       </c>
       <c r="H8" s="3">
-        <v>77677</v>
+        <v>79153</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -672,25 +672,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="3">
-        <v>102861</v>
+        <v>104815</v>
       </c>
       <c r="C9" s="3">
-        <v>137695</v>
+        <v>140311</v>
       </c>
       <c r="D9" s="3">
-        <v>181709</v>
+        <v>185161</v>
       </c>
       <c r="E9" s="3">
-        <v>348095</v>
+        <v>354709</v>
       </c>
       <c r="F9" s="3">
-        <v>510584</v>
+        <v>520285</v>
       </c>
       <c r="G9" s="3">
-        <v>97301</v>
+        <v>99150</v>
       </c>
       <c r="H9" s="3">
-        <v>91140</v>
+        <v>92872</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -698,25 +698,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="3">
-        <v>125362</v>
+        <v>127744</v>
       </c>
       <c r="C10" s="3">
-        <v>176225</v>
+        <v>179573</v>
       </c>
       <c r="D10" s="3">
-        <v>216434</v>
+        <v>220546</v>
       </c>
       <c r="E10" s="3">
-        <v>419079</v>
+        <v>427042</v>
       </c>
       <c r="F10" s="3">
-        <v>597468</v>
+        <v>608820</v>
       </c>
       <c r="G10" s="3">
-        <v>116893</v>
+        <v>119114</v>
       </c>
       <c r="H10" s="3">
-        <v>109494</v>
+        <v>111574</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -724,25 +724,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="3">
-        <v>104271</v>
+        <v>106252</v>
       </c>
       <c r="C11" s="3">
-        <v>133927</v>
+        <v>136472</v>
       </c>
       <c r="D11" s="3">
-        <v>176254</v>
+        <v>179603</v>
       </c>
       <c r="E11" s="3">
-        <v>298803</v>
+        <v>304480</v>
       </c>
       <c r="F11" s="3">
-        <v>515811</v>
+        <v>525611</v>
       </c>
       <c r="G11" s="3">
-        <v>90818</v>
+        <v>92544</v>
       </c>
       <c r="H11" s="3">
-        <v>78335</v>
+        <v>79823</v>
       </c>
     </row>
   </sheetData>
